--- a/Part2/Day 2/Day 2 PM/PRMLS_day2_exercise_1.xlsx
+++ b/Part2/Day 2/Day 2 PM/PRMLS_day2_exercise_1.xlsx
@@ -1,24 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cc.leung\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\75643\Desktop\ISY5002\Part2\Day 2\Day 2 PM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE07A7BD-9A54-4AC9-BFCC-78501531B06D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F918922A-3C7E-42BD-9B29-937F57C6A7C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Convolution" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="150000" concurrentCalc="0"/>
+  <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
       <x14:workbookPr defaultImageDpi="32767"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
       <mx:ArchID Flags="2"/>
@@ -46,11 +57,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="DengXian"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -63,6 +74,19 @@
       <sz val="12"/>
       <color theme="1" tint="0.249977111117893"/>
       <name val="Fira Sans"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="DengXian"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Fira Sans"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="16">
@@ -219,15 +243,15 @@
     <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium7"/>
@@ -506,38 +530,38 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:Z20"/>
-  <sheetFormatPr defaultColWidth="4.1640625" defaultRowHeight="25" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="4.15234375" defaultRowHeight="25" customHeight="1"/>
   <cols>
-    <col min="1" max="16384" width="4.1640625" style="1"/>
+    <col min="1" max="16384" width="4.15234375" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:26" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="J2" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="K2" s="18"/>
-      <c r="L2" s="18"/>
-      <c r="M2" s="18"/>
-      <c r="Q2" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="R2" s="18"/>
-      <c r="S2" s="18"/>
-      <c r="T2" s="18"/>
-      <c r="U2" s="18"/>
-      <c r="X2" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y2" s="18"/>
+    <row r="2" spans="2:26" ht="25" customHeight="1">
+      <c r="B2" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="J2" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
+      <c r="Q2" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="R2" s="17"/>
+      <c r="S2" s="17"/>
+      <c r="T2" s="17"/>
+      <c r="U2" s="17"/>
+      <c r="X2" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y2" s="17"/>
       <c r="Z2" s="6"/>
     </row>
-    <row r="4" spans="2:26" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:26" ht="25" customHeight="1">
       <c r="B4" s="7">
         <v>1</v>
       </c>
@@ -565,12 +589,22 @@
       <c r="M4" s="13">
         <v>1</v>
       </c>
-      <c r="Q4" s="16"/>
-      <c r="R4" s="16"/>
-      <c r="X4" s="17"/>
-      <c r="Y4" s="17"/>
-    </row>
-    <row r="5" spans="2:26" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Q4" s="16">
+        <v>8</v>
+      </c>
+      <c r="R4" s="16">
+        <v>10</v>
+      </c>
+      <c r="X4" s="18">
+        <f>SUM(Q4,Q10,Q16)</f>
+        <v>21</v>
+      </c>
+      <c r="Y4" s="18">
+        <f>SUM(R4,R10,R16)</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="2:26" ht="25" customHeight="1">
       <c r="B5" s="7">
         <v>1</v>
       </c>
@@ -598,12 +632,22 @@
       <c r="M5" s="14">
         <v>0</v>
       </c>
-      <c r="Q5" s="16"/>
-      <c r="R5" s="16"/>
-      <c r="X5" s="17"/>
-      <c r="Y5" s="17"/>
-    </row>
-    <row r="6" spans="2:26" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Q5" s="16">
+        <v>8</v>
+      </c>
+      <c r="R5" s="16">
+        <v>7</v>
+      </c>
+      <c r="X5" s="18">
+        <f t="shared" ref="X5:Y6" si="0">SUM(Q5,Q11,Q17)</f>
+        <v>36</v>
+      </c>
+      <c r="Y5" s="18">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="2:26" ht="25" customHeight="1">
       <c r="B6" s="7">
         <v>1</v>
       </c>
@@ -631,12 +675,22 @@
       <c r="M6" s="15">
         <v>1</v>
       </c>
-      <c r="Q6" s="16"/>
-      <c r="R6" s="16"/>
-      <c r="X6" s="17"/>
-      <c r="Y6" s="17"/>
-    </row>
-    <row r="7" spans="2:26" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Q6" s="16">
+        <v>9</v>
+      </c>
+      <c r="R6" s="16">
+        <v>7</v>
+      </c>
+      <c r="X6" s="18">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="Y6" s="18">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="2:26" ht="25" customHeight="1">
       <c r="B7" s="7">
         <v>2</v>
       </c>
@@ -653,7 +707,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="2:26" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:26" ht="25" customHeight="1">
       <c r="B8" s="7">
         <v>0</v>
       </c>
@@ -670,7 +724,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="2:26" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:26" ht="25" customHeight="1">
       <c r="B10" s="7">
         <v>1</v>
       </c>
@@ -698,10 +752,14 @@
       <c r="M10" s="13">
         <v>0</v>
       </c>
-      <c r="Q10" s="13"/>
-      <c r="R10" s="13"/>
-    </row>
-    <row r="11" spans="2:26" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Q10" s="13">
+        <v>6</v>
+      </c>
+      <c r="R10" s="13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="2:26" ht="25" customHeight="1">
       <c r="B11" s="7">
         <v>2</v>
       </c>
@@ -729,10 +787,14 @@
       <c r="M11" s="14">
         <v>1</v>
       </c>
-      <c r="Q11" s="13"/>
-      <c r="R11" s="13"/>
-    </row>
-    <row r="12" spans="2:26" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Q11" s="13">
+        <v>14</v>
+      </c>
+      <c r="R11" s="13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="2:26" ht="25" customHeight="1">
       <c r="B12" s="7">
         <v>3</v>
       </c>
@@ -760,10 +822,14 @@
       <c r="M12" s="15">
         <v>0</v>
       </c>
-      <c r="Q12" s="13"/>
-      <c r="R12" s="13"/>
-    </row>
-    <row r="13" spans="2:26" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Q12" s="13">
+        <v>7</v>
+      </c>
+      <c r="R12" s="13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="2:26" ht="25" customHeight="1">
       <c r="B13" s="7">
         <v>0</v>
       </c>
@@ -780,7 +846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:26" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:26" ht="25" customHeight="1">
       <c r="B14" s="7">
         <v>1</v>
       </c>
@@ -797,7 +863,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="2:26" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:26" ht="25" customHeight="1">
       <c r="B16" s="7">
         <v>0</v>
       </c>
@@ -825,10 +891,14 @@
       <c r="M16" s="13">
         <v>0</v>
       </c>
-      <c r="Q16" s="13"/>
-      <c r="R16" s="13"/>
-    </row>
-    <row r="17" spans="2:18" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Q16" s="13">
+        <v>7</v>
+      </c>
+      <c r="R16" s="13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="2:18" ht="25" customHeight="1">
       <c r="B17" s="7">
         <v>1</v>
       </c>
@@ -856,10 +926,14 @@
       <c r="M17" s="14">
         <v>1</v>
       </c>
-      <c r="Q17" s="13"/>
-      <c r="R17" s="13"/>
-    </row>
-    <row r="18" spans="2:18" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Q17" s="13">
+        <v>14</v>
+      </c>
+      <c r="R17" s="13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="2:18" ht="25" customHeight="1">
       <c r="B18" s="7">
         <v>1</v>
       </c>
@@ -887,10 +961,14 @@
       <c r="M18" s="15">
         <v>0</v>
       </c>
-      <c r="Q18" s="13"/>
-      <c r="R18" s="13"/>
-    </row>
-    <row r="19" spans="2:18" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Q18" s="13">
+        <v>11</v>
+      </c>
+      <c r="R18" s="13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="2:18" ht="25" customHeight="1">
       <c r="B19" s="7">
         <v>0</v>
       </c>
@@ -907,7 +985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:18" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:18" ht="25" customHeight="1">
       <c r="B20" s="7">
         <v>1</v>
       </c>
@@ -931,6 +1009,7 @@
     <mergeCell ref="Q2:U2"/>
     <mergeCell ref="X2:Y2"/>
   </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>